--- a/src/test/resources/TestDriver/Hearst_CDB/ActivityData/CDB_AP.xlsx
+++ b/src/test/resources/TestDriver/Hearst_CDB/ActivityData/CDB_AP.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,16 @@
           <t>standalone_price_policy</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>parent_child</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>parent_code</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -458,6 +468,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -478,6 +493,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CDB_PRTDIG_GIFT_US_1499</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -498,6 +523,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CDB_PRTDIG_GIFT_US_1499</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -518,6 +553,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -538,6 +578,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CDB_PRTDIG_US_New_1499</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -558,6 +608,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CDB_PRTDIG_US_New_1499</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -578,6 +638,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -596,6 +661,11 @@
       <c r="D9" t="inlineStr">
         <is>
           <t>DOLLAR_AMOUNT</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Parent</t>
         </is>
       </c>
     </row>
